--- a/Files/Madden26/IE/Season2/FreeAgency/Input/ContractOffer[].xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Input/ContractOffer[].xlsx
@@ -3171,796 +3171,796 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>00100001000100100000000000000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="B2" t="str">
-        <v>00100001000100100000000000000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C2" t="str">
-        <v>00100001000100100000000000000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="D2" t="str">
-        <v>00100001000100100000000010010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="E2" t="str">
-        <v>00100001000100100000000000000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F2" t="str">
-        <v>00100001000100100000000000000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="G2" t="str">
-        <v>00100001000100100000000000000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="H2" t="str">
-        <v>00100001000100100000000000000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="I2" t="str">
-        <v>00100001000100100000000010011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="J2" t="str">
-        <v>00100001000100100000000010011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="K2" t="str">
-        <v>00100001000100100000000000001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="L2" t="str">
-        <v>00100001000100100000000000001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="M2" t="str">
-        <v>00100001000100100000000000001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="N2" t="str">
-        <v>00100001000100100000000000001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="O2" t="str">
-        <v>00100001000100100000000000001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="P2" t="str">
-        <v>00100001000100100000000000001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="Q2" t="str">
-        <v>00100001000100100000000000010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="R2" t="str">
-        <v>00100001000100100000000000010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="S2" t="str">
-        <v>00100001000100100000000000010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="T2" t="str">
-        <v>00100001000100100000000010001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="U2" t="str">
-        <v>00100001000100100000000000010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="V2" t="str">
-        <v>00100001000100100000000000010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="W2" t="str">
-        <v>00100001000100100000000000010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="X2" t="str">
-        <v>00100001000100100000000000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="Y2" t="str">
-        <v>00100001000100100000000000011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="Z2" t="str">
-        <v>00100001000100100000000000011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AA2" t="str">
-        <v>00100001000100100000000010010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AB2" t="str">
-        <v>00100001000100100000000010011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AC2" t="str">
-        <v>00100001000100100000000000011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AD2" t="str">
-        <v>00100001000100100000000000011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AE2" t="str">
-        <v>00100001000100100000000010001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AF2" t="str">
-        <v>00100001000100100000000000011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AG2" t="str">
-        <v>00100001000100100000000000100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AH2" t="str">
-        <v>00100001000100100000000000100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AI2" t="str">
-        <v>00100001000100100000000000100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AJ2" t="str">
-        <v>00100001000100100000000000100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AK2" t="str">
-        <v>00100001000100100000000010001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AL2" t="str">
-        <v>00100001000100100000000000100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AM2" t="str">
-        <v>00100001000100100000000000100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AN2" t="str">
-        <v>00100001000100100000000000100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AO2" t="str">
-        <v>00100001000100100000000000101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AP2" t="str">
-        <v>00100001000100100000000000101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AQ2" t="str">
-        <v>00100001000100100000000000101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AR2" t="str">
-        <v>00100001000100100000000000101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AS2" t="str">
-        <v>00100001000100100000000000101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AT2" t="str">
-        <v>00100001000100100000000000101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AU2" t="str">
-        <v>00100001000100100000000010011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AV2" t="str">
-        <v>00100001000100100000000000101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AW2" t="str">
-        <v>00100001000100100000000000110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AX2" t="str">
-        <v>00100001000100100000000010001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AY2" t="str">
-        <v>00100001000100100000000010010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="AZ2" t="str">
-        <v>00100001000100100000000000110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BA2" t="str">
-        <v>00100001000100100000000010010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BB2" t="str">
-        <v>00100001000100100000000010010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BC2" t="str">
-        <v>00100001000100100000000000110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BD2" t="str">
-        <v>00100001000100100000000010000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BE2" t="str">
-        <v>00100001000100100000000000111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BF2" t="str">
-        <v>00100001000100100000000000111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BG2" t="str">
-        <v>00100001000100100000000000111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BH2" t="str">
-        <v>00100001000100100000000000111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BI2" t="str">
-        <v>00100001000100100000000000111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BJ2" t="str">
-        <v>00100001000100100000000001111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BK2" t="str">
-        <v>00100001000100100000000000111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BL2" t="str">
-        <v>00100001000100100000000000111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BM2" t="str">
-        <v>00100001000100100000000010011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BN2" t="str">
-        <v>00100001000100100000000010001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BO2" t="str">
-        <v>00100001000100100000000001000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BP2" t="str">
-        <v>00100001000100100000000010001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BQ2" t="str">
-        <v>00100001000100100000000001000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BR2" t="str">
-        <v>00100001000100100000000010010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BS2" t="str">
-        <v>00100001000100100000000001000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BT2" t="str">
-        <v>00100001000100100000000001000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BU2" t="str">
-        <v>00100001000100100000000001001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BV2" t="str">
-        <v>00100001000100100000000001001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BW2" t="str">
-        <v>00100001000100100000000001001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BX2" t="str">
-        <v>00100001000100100000000010100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BY2" t="str">
-        <v>00100001000100100000000001001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="BZ2" t="str">
-        <v>00100001000100100000000001001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CA2" t="str">
-        <v>00100001000100100000000001001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CB2" t="str">
-        <v>00100001000100100000000001001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CC2" t="str">
-        <v>00100001000100100000000001010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CD2" t="str">
-        <v>00100001000100100000000100000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CE2" t="str">
-        <v>00100001000100100000000001010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CF2" t="str">
-        <v>00100001000100100000000010001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CG2" t="str">
-        <v>00100001000100100000000001010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CH2" t="str">
-        <v>00100001000100100000000001010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CI2" t="str">
-        <v>00100001000100100000000001111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CJ2" t="str">
-        <v>00100001000100100000000100000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CK2" t="str">
-        <v>00100001000100100000000001111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CL2" t="str">
-        <v>00100001000100100000000001011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CM2" t="str">
-        <v>00100001000100100000000010000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CN2" t="str">
-        <v>00100001000100100000000001011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CO2" t="str">
-        <v>00100001000100100000000001011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CP2" t="str">
-        <v>00100001000100100000000001011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CQ2" t="str">
-        <v>00100001000100100000000010011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CR2" t="str">
-        <v>00100001000100100000000010011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CS2" t="str">
-        <v>00100001000100100000000001100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CT2" t="str">
-        <v>00100001000100100000000001100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CU2" t="str">
-        <v>00100001000100100000000010000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CV2" t="str">
-        <v>00100001000100100000000001100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CW2" t="str">
-        <v>00100001000100100000000001100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CX2" t="str">
-        <v>00100001000100100000000001100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CY2" t="str">
-        <v>00100001000100100000000001100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="CZ2" t="str">
-        <v>00100001000100100000000001100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DA2" t="str">
-        <v>00100001000100100000000001101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DB2" t="str">
-        <v>00100001000100100000000001101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DC2" t="str">
-        <v>00100001000100100000000010010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DD2" t="str">
-        <v>00100001000100100000000010010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DE2" t="str">
-        <v>00100001000100100000000001101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DF2" t="str">
-        <v>00100001000100100000000001111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DG2" t="str">
-        <v>00100001000100100000000001101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DH2" t="str">
-        <v>00100001000100100000000001101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DI2" t="str">
-        <v>00100001000100100000000001110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DJ2" t="str">
-        <v>00100001000100100000000001110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DK2" t="str">
-        <v>00100001000100100000000001110010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DL2" t="str">
-        <v>00100001000100100000000001110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DM2" t="str">
-        <v>00100001000100100000000001110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DN2" t="str">
-        <v>00100001000100100000000001110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DO2" t="str">
-        <v>00100001000100100000000001110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DP2" t="str">
-        <v>00100001000100100000000010001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DQ2" t="str">
-        <v>00100001000100100000000001111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DR2" t="str">
-        <v>00100001000100100000000001111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DS2" t="str">
-        <v>00100001000100100000000001111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DT2" t="str">
-        <v>00100001000100100000000000000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DU2" t="str">
-        <v>00100001000100100000000000001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DV2" t="str">
-        <v>00100001000100100000000000001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DW2" t="str">
-        <v>00100001000100100000000100001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DX2" t="str">
-        <v>00100001000100100000000000011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DY2" t="str">
-        <v>00100001000100100000000000011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="DZ2" t="str">
-        <v>00100001000100100000000000011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EA2" t="str">
-        <v>00100001000100100000000100010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EB2" t="str">
-        <v>00100001000100100000000000101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EC2" t="str">
-        <v>00100001000100100000000100011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="ED2" t="str">
-        <v>00100001000100100000000100100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EE2" t="str">
-        <v>00100001000100100000000000110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EF2" t="str">
-        <v>00100001000100100000000100001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EG2" t="str">
-        <v>00100001000100100000000100010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EH2" t="str">
-        <v>00100001000100100000000000111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EI2" t="str">
-        <v>00100001000100100000000001000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EJ2" t="str">
-        <v>00100001000100100000000001000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EK2" t="str">
-        <v>00100001000100100000000001000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EL2" t="str">
-        <v>00100001000100100000000001000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EM2" t="str">
-        <v>00100001000100100000000001001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EN2" t="str">
-        <v>00100001000100100000000001010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EO2" t="str">
-        <v>00100001000100100000000001010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EP2" t="str">
-        <v>00100001000100100000000001010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EQ2" t="str">
-        <v>00100001000100100000000100001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="ER2" t="str">
-        <v>00100001000100100000000001011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="ES2" t="str">
-        <v>00100001000100100000000001011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="ET2" t="str">
-        <v>00100001000100100000000001011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EU2" t="str">
-        <v>00100001000100100000000001011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EV2" t="str">
-        <v>00100001000100100000000001100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EW2" t="str">
-        <v>00100001000100100000000001101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EX2" t="str">
-        <v>00100001000100100000000001101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EY2" t="str">
-        <v>00100001000100100000000100011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="EZ2" t="str">
-        <v>00100001000100100000000100001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FA2" t="str">
-        <v>00100001000100100000000001111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FB2" t="str">
-        <v>00100001000100100000000010000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FC2" t="str">
-        <v>00100001000100100000000010000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FD2" t="str">
-        <v>00100001000100100000000010000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FE2" t="str">
-        <v>00100001000100100000000010000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FF2" t="str">
-        <v>00100001000100100000000010000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FG2" t="str">
-        <v>00100001000100100000000010011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FH2" t="str">
-        <v>00100001000100100000000100101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FI2" t="str">
-        <v>00100001000100100000000010100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FJ2" t="str">
-        <v>00100001000100100000000010100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FK2" t="str">
-        <v>00100001000100100000000010100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FL2" t="str">
-        <v>00100001000100100000000100010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FM2" t="str">
-        <v>00100001000100100000000010100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FN2" t="str">
-        <v>00100001000100100000000010100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FO2" t="str">
-        <v>00100001000100100000000010101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FP2" t="str">
-        <v>00100001000100100000000010101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FQ2" t="str">
-        <v>00100001000100100000000010101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FR2" t="str">
-        <v>00100001000100100000000010101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FS2" t="str">
-        <v>00100001000100100000000010101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FT2" t="str">
-        <v>00100001000100100000000010101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FU2" t="str">
-        <v>00100001000100100000000010101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FV2" t="str">
-        <v>00100001000100100000000100001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FW2" t="str">
-        <v>00100001000100100000000100010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FX2" t="str">
-        <v>00100001000100100000000100101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FY2" t="str">
-        <v>00100001000100100000000010110010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="FZ2" t="str">
-        <v>00100001000100100000000010110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GA2" t="str">
-        <v>00100001000100100000000010110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GB2" t="str">
-        <v>00100001000100100000000010110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GC2" t="str">
-        <v>00100001000100100000000010110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GD2" t="str">
-        <v>00100001000100100000000010110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GE2" t="str">
-        <v>00100001000100100000000010111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GF2" t="str">
-        <v>00100001000100100000000010111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GG2" t="str">
-        <v>00100001000100100000000010111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GH2" t="str">
-        <v>00100001000100100000000100100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GI2" t="str">
-        <v>00100001000100100000000010111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GJ2" t="str">
-        <v>00100001000100100000000010111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GK2" t="str">
-        <v>00100001000100100000000010111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GL2" t="str">
-        <v>00100001000100100000000100100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GM2" t="str">
-        <v>00100001000100100000000011000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GN2" t="str">
-        <v>00100001000100100000000011000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GO2" t="str">
-        <v>00100001000100100000000011000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GP2" t="str">
-        <v>00100001000100100000000100001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GQ2" t="str">
-        <v>00100001000100100000000011000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GR2" t="str">
-        <v>00100001000100100000000011000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GS2" t="str">
-        <v>00100001000100100000000011000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GT2" t="str">
-        <v>00100001000100100000000100100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GU2" t="str">
-        <v>00100001000100100000000100010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GV2" t="str">
-        <v>00100001000100100000000011001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GW2" t="str">
-        <v>00100001000100100000000011001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GX2" t="str">
-        <v>00100001000100100000000011001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GY2" t="str">
-        <v>00100001000100100000000011001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="GZ2" t="str">
-        <v>00100001000100100000000011001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HA2" t="str">
-        <v>00100001000100100000000011001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HB2" t="str">
-        <v>00100001000100100000000011001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HC2" t="str">
-        <v>00100001000100100000000011010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HD2" t="str">
-        <v>00100001000100100000000011010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HE2" t="str">
-        <v>00100001000100100000000011010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HF2" t="str">
-        <v>00100001000100100000000100100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HG2" t="str">
-        <v>00100001000100100000000100010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HH2" t="str">
-        <v>00100001000100100000000011010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HI2" t="str">
-        <v>00100001000100100000000011010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HJ2" t="str">
-        <v>00100001000100100000000100001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HK2" t="str">
-        <v>00100001000100100000000011011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HL2" t="str">
-        <v>00100001000100100000000100011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HM2" t="str">
-        <v>00100001000100100000000011011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HN2" t="str">
-        <v>00100001000100100000000011011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HO2" t="str">
-        <v>00100001000100100000000100010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HP2" t="str">
-        <v>00100001000100100000000100100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HQ2" t="str">
-        <v>00100001000100100000000011011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HR2" t="str">
-        <v>00100001000100100000000011011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HS2" t="str">
-        <v>00100001000100100000000011100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HT2" t="str">
-        <v>00100001000100100000000100010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HU2" t="str">
-        <v>00100001000100100000000011100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HV2" t="str">
-        <v>00100001000100100000000011100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HW2" t="str">
-        <v>00100001000100100000000011100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HX2" t="str">
-        <v>00100001000100100000000011100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HY2" t="str">
-        <v>00100001000100100000000011100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="HZ2" t="str">
-        <v>00100001000100100000000011100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IA2" t="str">
-        <v>00100001000100100000000011101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IB2" t="str">
-        <v>00100001000100100000000011101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IC2" t="str">
-        <v>00100001000100100000000011101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="ID2" t="str">
-        <v>00100001000100100000000011101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IE2" t="str">
-        <v>00100001000100100000000011101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IF2" t="str">
-        <v>00100001000100100000000011101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IG2" t="str">
-        <v>00100001000100100000000100011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IH2" t="str">
-        <v>00100001000100100000000011101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="II2" t="str">
-        <v>00100001000100100000000011110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IJ2" t="str">
-        <v>00100001000100100000000011110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IK2" t="str">
-        <v>00100001000100100000000100001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IL2" t="str">
-        <v>00100001000100100000000011110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IM2" t="str">
-        <v>00100001000100100000000011110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IN2" t="str">
-        <v>00100001000100100000000011110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IO2" t="str">
-        <v>00100001000100100000000011110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IP2" t="str">
-        <v>00100001000100100000000011110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IQ2" t="str">
-        <v>00100001000100100000000011111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IR2" t="str">
-        <v>00100001000100100000000011111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IS2" t="str">
-        <v>00100001000100100000000011111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IT2" t="str">
-        <v>00100001000100100000000011111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IU2" t="str">
-        <v>00100001000100100000000100011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IV2" t="str">
-        <v>00100001000100100000000011111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IW2" t="str">
-        <v>00100001000100100000000011111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IX2" t="str">
-        <v>00100001000100100000000100100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IY2" t="str">
-        <v>00100001000100100000000100000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="IZ2" t="str">
-        <v>00100001000100100000000100100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="JA2" t="str">
-        <v>00100001000100100000000100000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="JB2" t="str">
-        <v>00100001000100100000000100000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="JC2" t="str">
-        <v>00100001000100100000000100000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="JD2" t="str">
-        <v>00100001000100100000000100000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="JE2" t="str">
         <v>00000000000000000000000000000000</v>
